--- a/evergreen_yp/data-collection/modbus_reader/pcs/pcs_1/modbus_config/fimer_pcs_1_modbus_address.xlsx
+++ b/evergreen_yp/data-collection/modbus_reader/pcs/pcs_1/modbus_config/fimer_pcs_1_modbus_address.xlsx
@@ -1,209 +1,218 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chingjenchen/Dropbox/FEMC/Field Deploy/field-deploy/evergreen_yp/data-collection/modbus_reader/pcs/pcs_1/modbus_config/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94FBE9E-AC33-864C-AE9B-2B652EE0FE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-51200" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Connection Config" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Modbus Address" sheetId="2" r:id="rId6"/>
+    <sheet name="Connection Config" sheetId="1" r:id="rId1"/>
+    <sheet name="Modbus Address" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="225">
   <si>
-    <t xml:space="preserve">Connection Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device Brand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fimer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCS_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.168.100.103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filesystem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">display name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fix value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bit length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signed type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endianness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal places</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enable bit configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bit configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enable parse configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parse configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is warning variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warning level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">start address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is heartbeat address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heartbeat interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">heartbeat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unsigned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Big Endian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">false</t>
-  </si>
-  <si>
-    <t xml:space="preserve">control_word</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>Connection Type</t>
+  </si>
+  <si>
+    <t>Device Brand</t>
+  </si>
+  <si>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Device Type</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Destination Location</t>
+  </si>
+  <si>
+    <t>TCP</t>
+  </si>
+  <si>
+    <t>Fimer</t>
+  </si>
+  <si>
+    <t>PCS_1</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>192.168.100.103</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>filesystem</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>address type</t>
+  </si>
+  <si>
+    <t>unit id</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>code name</t>
+  </si>
+  <si>
+    <t>display name</t>
+  </si>
+  <si>
+    <t>address name</t>
+  </si>
+  <si>
+    <t>function code</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>fix value</t>
+  </si>
+  <si>
+    <t>data type</t>
+  </si>
+  <si>
+    <t>bit length</t>
+  </si>
+  <si>
+    <t>signed type</t>
+  </si>
+  <si>
+    <t>endianness</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>decimal places</t>
+  </si>
+  <si>
+    <t>offset</t>
+  </si>
+  <si>
+    <t>enable bit configuration</t>
+  </si>
+  <si>
+    <t>bit configuration</t>
+  </si>
+  <si>
+    <t>enable parse configuration</t>
+  </si>
+  <si>
+    <t>parse configuration</t>
+  </si>
+  <si>
+    <t>is warning variable</t>
+  </si>
+  <si>
+    <t>warning level</t>
+  </si>
+  <si>
+    <t>start address</t>
+  </si>
+  <si>
+    <t>data count</t>
+  </si>
+  <si>
+    <t>is heartbeat address</t>
+  </si>
+  <si>
+    <t>heartbeat interval</t>
+  </si>
+  <si>
+    <t>individual</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>heartbeat</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>42240</t>
+  </si>
+  <si>
+    <t>Int</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Unsigned</t>
+  </si>
+  <si>
+    <t>Big Endian</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>control_word</t>
+  </si>
+  <si>
+    <t>42241</t>
+  </si>
+  <si>
+    <t>Bit</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "",
     "displayName": "逆變器操作:",
@@ -303,136 +312,136 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">p_ref_operation_mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q_ref_operation_mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">setting_power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">setting_reactive_power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">setting_active_power_percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Double</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">setting_reactive_power_percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">setting_power_factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vac_reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_power_percent_limit_to_grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_power_percent_limit_from_grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reactive_current_positive_percent_limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reactive_current_negative_percent_limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">user_ac_voltage_ref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drooping_q_power_offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">user_frequency_ref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drooping_power_offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set_heartbeat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">running_status_code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">running_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[
+    <t>p_ref_operation_mode</t>
+  </si>
+  <si>
+    <t>42242</t>
+  </si>
+  <si>
+    <t>q_ref_operation_mode</t>
+  </si>
+  <si>
+    <t>42243</t>
+  </si>
+  <si>
+    <t>setting_power</t>
+  </si>
+  <si>
+    <t>42244</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>setting_reactive_power</t>
+  </si>
+  <si>
+    <t>42245</t>
+  </si>
+  <si>
+    <t>setting_active_power_percent</t>
+  </si>
+  <si>
+    <t>42246</t>
+  </si>
+  <si>
+    <t>Double</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>setting_reactive_power_percent</t>
+  </si>
+  <si>
+    <t>42247</t>
+  </si>
+  <si>
+    <t>setting_power_factor</t>
+  </si>
+  <si>
+    <t>42248</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>vac_reference</t>
+  </si>
+  <si>
+    <t>42249</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>active_power_percent_limit_to_grid</t>
+  </si>
+  <si>
+    <t>42250</t>
+  </si>
+  <si>
+    <t>active_power_percent_limit_from_grid</t>
+  </si>
+  <si>
+    <t>42251</t>
+  </si>
+  <si>
+    <t>reactive_current_positive_percent_limit</t>
+  </si>
+  <si>
+    <t>42252</t>
+  </si>
+  <si>
+    <t>reactive_current_negative_percent_limit</t>
+  </si>
+  <si>
+    <t>42253</t>
+  </si>
+  <si>
+    <t>user_ac_voltage_ref</t>
+  </si>
+  <si>
+    <t>42254</t>
+  </si>
+  <si>
+    <t>drooping_q_power_offset</t>
+  </si>
+  <si>
+    <t>42255</t>
+  </si>
+  <si>
+    <t>user_frequency_ref</t>
+  </si>
+  <si>
+    <t>42256</t>
+  </si>
+  <si>
+    <t>drooping_power_offset</t>
+  </si>
+  <si>
+    <t>42257</t>
+  </si>
+  <si>
+    <t>set_heartbeat</t>
+  </si>
+  <si>
+    <t>42496</t>
+  </si>
+  <si>
+    <t>running_status_code</t>
+  </si>
+  <si>
+    <t>42497</t>
+  </si>
+  <si>
+    <t>running_status</t>
+  </si>
+  <si>
+    <t>[
   {
     "input": "0",
     "output": "待機"
@@ -472,211 +481,211 @@
 ]</t>
   </si>
   <si>
-    <t xml:space="preserve">active_power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reactive_power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volt_avg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battery_voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_power_limit_to_grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_power_limit_from_grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive_reactive_power_limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative_reactive_power_limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_fault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volt_rs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volt_st</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volt_tr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">current_r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">current_s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">current_t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dc_active_power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dc_grounding_current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dc_isolation_resistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ambient_temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">igbt_temp_m1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ctrl_section_temp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cabinet_temp_m1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lcl_section_temp_m1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">humidity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kwh_energy_charged_to_battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mwh_energy_charged_to_battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gwh_energy_charged_to_battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kwh_energy_discharged_from_battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mwh_energy_discharged_from_battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gwh_energy_discharged_from_battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">array</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dc_input_current_m1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele_switching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>active_power</t>
+  </si>
+  <si>
+    <t>42498</t>
+  </si>
+  <si>
+    <t>reactive_power</t>
+  </si>
+  <si>
+    <t>42499</t>
+  </si>
+  <si>
+    <t>volt_avg</t>
+  </si>
+  <si>
+    <t>42500</t>
+  </si>
+  <si>
+    <t>frequency</t>
+  </si>
+  <si>
+    <t>42501</t>
+  </si>
+  <si>
+    <t>battery_voltage</t>
+  </si>
+  <si>
+    <t>42502</t>
+  </si>
+  <si>
+    <t>active_power_limit_to_grid</t>
+  </si>
+  <si>
+    <t>42503</t>
+  </si>
+  <si>
+    <t>active_power_limit_from_grid</t>
+  </si>
+  <si>
+    <t>42504</t>
+  </si>
+  <si>
+    <t>positive_reactive_power_limit</t>
+  </si>
+  <si>
+    <t>42505</t>
+  </si>
+  <si>
+    <t>negative_reactive_power_limit</t>
+  </si>
+  <si>
+    <t>42506</t>
+  </si>
+  <si>
+    <t>active_fault</t>
+  </si>
+  <si>
+    <t>42545</t>
+  </si>
+  <si>
+    <t>volt_rs</t>
+  </si>
+  <si>
+    <t>42546</t>
+  </si>
+  <si>
+    <t>volt_st</t>
+  </si>
+  <si>
+    <t>42547</t>
+  </si>
+  <si>
+    <t>volt_tr</t>
+  </si>
+  <si>
+    <t>42548</t>
+  </si>
+  <si>
+    <t>current_r</t>
+  </si>
+  <si>
+    <t>42549</t>
+  </si>
+  <si>
+    <t>current_s</t>
+  </si>
+  <si>
+    <t>42550</t>
+  </si>
+  <si>
+    <t>current_t</t>
+  </si>
+  <si>
+    <t>42551</t>
+  </si>
+  <si>
+    <t>dc_active_power</t>
+  </si>
+  <si>
+    <t>42552</t>
+  </si>
+  <si>
+    <t>dc_grounding_current</t>
+  </si>
+  <si>
+    <t>42557</t>
+  </si>
+  <si>
+    <t>dc_isolation_resistance</t>
+  </si>
+  <si>
+    <t>42558</t>
+  </si>
+  <si>
+    <t>ambient_temperature</t>
+  </si>
+  <si>
+    <t>42559</t>
+  </si>
+  <si>
+    <t>igbt_temp_m1</t>
+  </si>
+  <si>
+    <t>42560</t>
+  </si>
+  <si>
+    <t>ctrl_section_temp</t>
+  </si>
+  <si>
+    <t>42564</t>
+  </si>
+  <si>
+    <t>cabinet_temp_m1</t>
+  </si>
+  <si>
+    <t>42565</t>
+  </si>
+  <si>
+    <t>lcl_section_temp_m1</t>
+  </si>
+  <si>
+    <t>42569</t>
+  </si>
+  <si>
+    <t>humidity</t>
+  </si>
+  <si>
+    <t>42573</t>
+  </si>
+  <si>
+    <t>kwh_energy_charged_to_battery</t>
+  </si>
+  <si>
+    <t>42574</t>
+  </si>
+  <si>
+    <t>mwh_energy_charged_to_battery</t>
+  </si>
+  <si>
+    <t>42575</t>
+  </si>
+  <si>
+    <t>gwh_energy_charged_to_battery</t>
+  </si>
+  <si>
+    <t>42576</t>
+  </si>
+  <si>
+    <t>kwh_energy_discharged_from_battery</t>
+  </si>
+  <si>
+    <t>42577</t>
+  </si>
+  <si>
+    <t>mwh_energy_discharged_from_battery</t>
+  </si>
+  <si>
+    <t>42578</t>
+  </si>
+  <si>
+    <t>gwh_energy_discharged_from_battery</t>
+  </si>
+  <si>
+    <t>42579</t>
+  </si>
+  <si>
+    <t>array</t>
+  </si>
+  <si>
+    <t>dc_input_current_m1</t>
+  </si>
+  <si>
+    <t>42582</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>ele_switching</t>
+  </si>
+  <si>
+    <t>42630</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "",
     "displayName": "AC_M1接觸器:",
@@ -776,13 +785,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">ele_switching_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>ele_switching_2</t>
+  </si>
+  <si>
+    <t>42631</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "",
     "displayName": "",
@@ -882,13 +891,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">inverter_main_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>inverter_main_status</t>
+  </si>
+  <si>
+    <t>42632</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "",
     "displayName": "",
@@ -988,13 +997,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">limitation_status_word</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>limitation_status_word</t>
+  </si>
+  <si>
+    <t>42633</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "IGBT_TEMP_LIMITATION",
     "displayName": "功率受限(IGBT Temp.)",
@@ -1094,13 +1103,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">grid_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>grid_status</t>
+  </si>
+  <si>
+    <t>42636</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "",
     "displayName": "電網欠壓",
@@ -1200,13 +1209,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">fan_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>fan_status</t>
+  </si>
+  <si>
+    <t>42637</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "",
     "displayName": "通道1_風扇#1:",
@@ -1306,13 +1315,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">fan_status2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>fan_status2</t>
+  </si>
+  <si>
+    <t>42638</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "",
     "displayName": "LCL_M1風扇#1:",
@@ -1412,19 +1421,19 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">env_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fault_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>env_status</t>
+  </si>
+  <si>
+    <t>42639</t>
+  </si>
+  <si>
+    <t>fault_status</t>
+  </si>
+  <si>
+    <t>42640</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "FAST_POWER_OFF",
     "displayName": "快速關機(0x6E1C)",
@@ -1524,13 +1533,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">fault_status2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>fault_status2</t>
+  </si>
+  <si>
+    <t>42641</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "48V_BUFFER_FAULT",
     "displayName": "48V緩衝器故障(0x9133)",
@@ -1630,13 +1639,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">warning_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>warning_status</t>
+  </si>
+  <si>
+    <t>42642</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "GROUNDING_CURRENT_WARNING",
     "displayName": "接地電流突變告警(0xE104)",
@@ -1736,13 +1745,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">dc_fuse_m1_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>dc_fuse_m1_status</t>
+  </si>
+  <si>
+    <t>42647</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "DC_M1_FUSE_1_FAULT",
     "displayName": "DC_M1保險絲1失效",
@@ -1842,13 +1851,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">dc_fuse_m2_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>dc_fuse_m2_status</t>
+  </si>
+  <si>
+    <t>42648</t>
+  </si>
+  <si>
+    <t>{
   "bit0": {
     "codeName": "DC_M2_FUSE_1_FAULT",
     "displayName": "DC_M2保險絲1失效",
@@ -1948,90 +1957,103 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">inverter_inhibits_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inverter_inhibits_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apparent_power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nominal_grid_voltage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">serial_number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">set_output_heartbeat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
+    <t>inverter_inhibits_1</t>
+  </si>
+  <si>
+    <t>42651</t>
+  </si>
+  <si>
+    <t>inverter_inhibits_2</t>
+  </si>
+  <si>
+    <t>42652</t>
+  </si>
+  <si>
+    <t>apparent_power</t>
+  </si>
+  <si>
+    <t>42653</t>
+  </si>
+  <si>
+    <t>nominal_grid_voltage</t>
+  </si>
+  <si>
+    <t>42654</t>
+  </si>
+  <si>
+    <t>serial_number</t>
+  </si>
+  <si>
+    <t>42655</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>set_output_heartbeat</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2221,14 +2243,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2260,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -2298,10 +2335,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -2381,7 +2419,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
@@ -2461,7 +2499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
@@ -2541,7 +2579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>46</v>
       </c>
@@ -2621,7 +2659,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
@@ -2701,7 +2739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
@@ -2781,7 +2819,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -2861,7 +2899,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -2941,7 +2979,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>46</v>
       </c>
@@ -3021,7 +3059,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
@@ -3101,7 +3139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
@@ -3181,7 +3219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
@@ -3261,7 +3299,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
@@ -3341,7 +3379,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
@@ -3421,7 +3459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
@@ -3501,7 +3539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -3581,7 +3619,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -3661,7 +3699,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>46</v>
       </c>
@@ -3741,7 +3779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
@@ -3821,7 +3859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
@@ -3901,7 +3939,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -3981,7 +4019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
@@ -4061,7 +4099,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
@@ -4141,7 +4179,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -4221,7 +4259,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>46</v>
       </c>
@@ -4301,7 +4339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
@@ -4381,7 +4419,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -4461,7 +4499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>46</v>
       </c>
@@ -4541,7 +4579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>46</v>
       </c>
@@ -4621,7 +4659,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>46</v>
       </c>
@@ -4701,7 +4739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>46</v>
       </c>
@@ -4781,7 +4819,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>46</v>
       </c>
@@ -4861,7 +4899,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>46</v>
       </c>
@@ -4941,7 +4979,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>46</v>
       </c>
@@ -5021,7 +5059,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>46</v>
       </c>
@@ -5101,7 +5139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -5181,7 +5219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
@@ -5261,7 +5299,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -5341,7 +5379,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>46</v>
       </c>
@@ -5421,7 +5459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -5501,7 +5539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>46</v>
       </c>
@@ -5581,7 +5619,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>46</v>
       </c>
@@ -5661,7 +5699,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -5741,7 +5779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>46</v>
       </c>
@@ -5821,7 +5859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -5901,7 +5939,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -5981,7 +6019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
@@ -6061,7 +6099,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -6141,7 +6179,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>46</v>
       </c>
@@ -6221,7 +6259,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>46</v>
       </c>
@@ -6301,7 +6339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>46</v>
       </c>
@@ -6381,7 +6419,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>46</v>
       </c>
@@ -6461,7 +6499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>46</v>
       </c>
@@ -6541,7 +6579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>170</v>
       </c>
@@ -6621,7 +6659,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>46</v>
       </c>
@@ -6701,7 +6739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>46</v>
       </c>
@@ -6781,7 +6819,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>46</v>
       </c>
@@ -6861,7 +6899,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>46</v>
       </c>
@@ -6941,7 +6979,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>46</v>
       </c>
@@ -7021,7 +7059,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>46</v>
       </c>
@@ -7101,7 +7139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>46</v>
       </c>
@@ -7181,7 +7219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>46</v>
       </c>
@@ -7261,7 +7299,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>46</v>
       </c>
@@ -7341,7 +7379,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>46</v>
       </c>
@@ -7421,7 +7459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>46</v>
       </c>
@@ -7501,7 +7539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>46</v>
       </c>
@@ -7581,7 +7619,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>46</v>
       </c>
@@ -7661,7 +7699,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>46</v>
       </c>
@@ -7741,7 +7779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>46</v>
       </c>
@@ -7821,7 +7859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>46</v>
       </c>
@@ -7901,7 +7939,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>46</v>
       </c>
@@ -7981,7 +8019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>46</v>
       </c>
@@ -8061,7 +8099,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>46</v>
       </c>
